--- a/data-manipulation-scripts/sheets-cleanup/sheets/ALAVANCA FREIO 06_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/ALAVANCA FREIO 06_02.xlsx
@@ -46,7 +46,7 @@
     <t>070341179109</t>
   </si>
   <si>
-    <t>ALAVANCA FREIO MANICOTO IRON YBR125/ RD135 350243</t>
+    <t>ALAVANCA FREIO IRON YBR125/ RD135 350243</t>
   </si>
 </sst>
 </file>
@@ -352,7 +352,9 @@
       <c r="C2" s="2">
         <v>5.0</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>22.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -364,7 +366,9 @@
       <c r="C3" s="2">
         <v>4.0</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>22.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -376,7 +380,9 @@
       <c r="C4" s="2">
         <v>4.0</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>22.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -386,7 +392,9 @@
         <v>11</v>
       </c>
       <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="D5" s="2">
+        <v>22.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4"/>
